--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.00662655017572</v>
+        <v>8.613576814403554</v>
       </c>
       <c r="D2" t="n">
-        <v>51.37343074028843</v>
+        <v>8.348182495296872</v>
       </c>
       <c r="E2" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.51378084756324</v>
+        <v>10.97098938772903</v>
       </c>
       <c r="D3" t="n">
-        <v>66.66110415872821</v>
+        <v>10.83242942579333</v>
       </c>
       <c r="E3" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F3" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.37467136333542</v>
+        <v>8.185884096542006</v>
       </c>
       <c r="D4" t="n">
-        <v>50.21922211927868</v>
+        <v>8.160623594382786</v>
       </c>
       <c r="E4" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F4" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.27356835017098</v>
+        <v>5.244454856902784</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56100663846968</v>
+        <v>5.128663578751324</v>
       </c>
       <c r="E5" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F5" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>87.57438480857208</v>
+        <v>14.23083753139296</v>
       </c>
       <c r="D6" t="n">
-        <v>58.9414864607993</v>
+        <v>9.577991549879886</v>
       </c>
       <c r="E6" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F6" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.67865302047176</v>
+        <v>9.697781115826661</v>
       </c>
       <c r="D7" t="n">
-        <v>59.40266032311963</v>
+        <v>9.65293230250694</v>
       </c>
       <c r="E7" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F7" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.42032008985184</v>
+        <v>7.705802014600924</v>
       </c>
       <c r="D8" t="n">
-        <v>47.38683268640974</v>
+        <v>7.700360311541583</v>
       </c>
       <c r="E8" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F8" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.94751418393455</v>
+        <v>8.116471054889365</v>
       </c>
       <c r="D9" t="n">
-        <v>48.83498076577101</v>
+        <v>7.93568437443779</v>
       </c>
       <c r="E9" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F9" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.5661983545157</v>
+        <v>5.617007232608802</v>
       </c>
       <c r="D10" t="n">
-        <v>32.15358270457406</v>
+        <v>5.224957189493286</v>
       </c>
       <c r="E10" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F10" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>56.74269407731088</v>
+        <v>9.220687787563019</v>
       </c>
       <c r="D11" t="n">
-        <v>54.53133000811397</v>
+        <v>8.86134112631852</v>
       </c>
       <c r="E11" t="n">
-        <v>15.07681955525575</v>
+        <v>2.44998317772906</v>
       </c>
       <c r="F11" t="n">
-        <v>10.65355976471465</v>
+        <v>1.73120346176613</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
